--- a/examples/recipes.xlsx
+++ b/examples/recipes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1848"/>
+  <dimension ref="A1:F1854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18000,18 +18000,18 @@
         </is>
       </c>
       <c r="C676" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>[{'name': 'Item_FatbergChunk', 'quantity': 2, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 2, 'artwork': '-760002536937637001'}]</t>
+          <t>[{'name': 'Item_FatbergChunk', 'quantity': 3, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 2, 'artwork': '-760002536937637001'}]</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="F676" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
     </row>
     <row r="677">
@@ -18026,18 +18026,18 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>[{'name': 'Item_FatbergChunk', 'quantity': 2, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 2, 'artwork': '-760002536937637001'}]</t>
+          <t>[{'name': 'Item_FatbergChunk', 'quantity': 2, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 3, 'artwork': '-760002536937637001'}]</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="F677" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="678">
@@ -18052,18 +18052,18 @@
         </is>
       </c>
       <c r="C678" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>[{'name': 'Item_FatbergChunk', 'quantity': 4, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 4, 'artwork': '-760002536937637001'}]</t>
+          <t>[{'name': 'Item_FatbergChunk', 'quantity': 3, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 3, 'artwork': '-760002536937637001'}]</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="F678" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
     </row>
     <row r="679">
@@ -48484,6 +48484,162 @@
       </c>
       <c r="F1848" t="n">
         <v>240</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>Recipe_Pilk</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>Item_Pilk</t>
+        </is>
+      </c>
+      <c r="C1849" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_MilkBlue', 'quantity': 1, 'artwork': '-7453886484582297559'}, {'name': 'Item_SulfCola', 'quantity': 1, 'artwork': '3619831582933252452'}]</t>
+        </is>
+      </c>
+      <c r="E1849" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>Recipe_Pilk2</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>Item_Pilk</t>
+        </is>
+      </c>
+      <c r="C1850" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_MilkGreen', 'quantity': 1, 'artwork': '-1859587392189770639'}, {'name': 'Item_SulfCola', 'quantity': 1, 'artwork': '3619831582933252452'}]</t>
+        </is>
+      </c>
+      <c r="E1850" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>Recipe_Pilk3</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Item_Pilk</t>
+        </is>
+      </c>
+      <c r="C1851" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_MilkRed', 'quantity': 1, 'artwork': '-7247210019374005315'}, {'name': 'Item_SulfCola', 'quantity': 1, 'artwork': '3619831582933252452'}]</t>
+        </is>
+      </c>
+      <c r="E1851" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>Recipe_SulfCola_1</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>Item_SulfCola</t>
+        </is>
+      </c>
+      <c r="C1852" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_BottledWater', 'quantity': 1, 'artwork': '-7066971589872746693'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]</t>
+        </is>
+      </c>
+      <c r="E1852" t="n">
+        <v>900</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>Recipe_SulfCola_2</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Item_SulfCola</t>
+        </is>
+      </c>
+      <c r="C1853" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_MineralWater', 'quantity': 1, 'artwork': '634777362706650203'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]</t>
+        </is>
+      </c>
+      <c r="E1853" t="n">
+        <v>900</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>Recipe_SulfCola_3</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Item_SulfCola</t>
+        </is>
+      </c>
+      <c r="C1854" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_HolyWater', 'quantity': 1, 'artwork': '8470882321417267426'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]</t>
+        </is>
+      </c>
+      <c r="E1854" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -48497,7 +48653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FF186"/>
+  <dimension ref="A1:FF188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -53186,17 +53342,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_FatbergChunk', 'quantity': 2, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 2, 'artwork': '-760002536937637001'}]}</t>
+          <t>{'quantity': 5, 'itemsNeeded': [{'name': 'Item_FatbergChunk', 'quantity': 3, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 2, 'artwork': '-760002536937637001'}]}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_FatbergChunk', 'quantity': 2, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 2, 'artwork': '-760002536937637001'}]}</t>
+          <t>{'quantity': 5, 'itemsNeeded': [{'name': 'Item_FatbergChunk', 'quantity': 2, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 3, 'artwork': '-760002536937637001'}]}</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{'quantity': 4, 'itemsNeeded': [{'name': 'Item_FatbergChunk', 'quantity': 4, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 4, 'artwork': '-760002536937637001'}]}</t>
+          <t>{'quantity': 6, 'itemsNeeded': [{'name': 'Item_FatbergChunk', 'quantity': 3, 'artwork': '2551009402558895804'}, {'name': 'Item_Sugar', 'quantity': 3, 'artwork': '-760002536937637001'}]}</t>
         </is>
       </c>
     </row>
@@ -59676,6 +59832,50 @@
       <c r="E186" t="inlineStr">
         <is>
           <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Item_Paper', 'quantity': 2, 'artwork': '-2332595742282668570'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Item_Pilk</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Item_MilkBlue', 'quantity': 1, 'artwork': '-7453886484582297559'}, {'name': 'Item_SulfCola', 'quantity': 1, 'artwork': '3619831582933252452'}]}</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Item_MilkGreen', 'quantity': 1, 'artwork': '-1859587392189770639'}, {'name': 'Item_SulfCola', 'quantity': 1, 'artwork': '3619831582933252452'}]}</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Item_MilkRed', 'quantity': 1, 'artwork': '-7247210019374005315'}, {'name': 'Item_SulfCola', 'quantity': 1, 'artwork': '3619831582933252452'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>Item_SulfCola</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_BottledWater', 'quantity': 1, 'artwork': '-7066971589872746693'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]}</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_MineralWater', 'quantity': 1, 'artwork': '634777362706650203'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]}</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>{'quantity': 5, 'itemsNeeded': [{'name': 'Item_HolyWater', 'quantity': 1, 'artwork': '8470882321417267426'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]}</t>
         </is>
       </c>
     </row>

--- a/examples/recipes.xlsx
+++ b/examples/recipes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1853"/>
+  <dimension ref="A1:F1866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -48616,6 +48616,344 @@
         <v>830</v>
       </c>
     </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>Recipe_Enchantment_SacredGround</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Enchantment_SacredGround</t>
+        </is>
+      </c>
+      <c r="C1854" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>[{'name': 'Enchantment_Earth', 'quantity': 1, 'artwork': '-5272188385312275718'}, {'name': 'Enchantment_Light', 'quantity': 1, 'artwork': '2352091176121211133'}]</t>
+        </is>
+      </c>
+      <c r="E1854" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>Recipe_BeefJerky_6</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>Item_BeefJerky</t>
+        </is>
+      </c>
+      <c r="C1855" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_LizardSkin', 'quantity': 2, 'artwork': '-2438037773057512394'}]</t>
+        </is>
+      </c>
+      <c r="E1855" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1855" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>Recipe_Enchantment_FoulFate</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Enchantment_FoulFate</t>
+        </is>
+      </c>
+      <c r="C1856" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>[{'name': 'Enchantment_Dark', 'quantity': 2, 'artwork': '7954706189709371483'}]</t>
+        </is>
+      </c>
+      <c r="E1856" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F1856" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>Recipe_Enchantment_Pollen</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>Enchantment_Pollen</t>
+        </is>
+      </c>
+      <c r="C1857" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>[{'name': 'Enchantment_Nature', 'quantity': 1, 'artwork': '2645463031653542284'}, {'name': 'Enchantment_Poison', 'quantity': 1, 'artwork': '992235308759174831'}]</t>
+        </is>
+      </c>
+      <c r="E1857" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F1857" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 1</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1858" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Coffee', 'quantity': 1, 'artwork': '4121941290723269396'}]</t>
+        </is>
+      </c>
+      <c r="E1858" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1858" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 2</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1859" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_BananaSulfs', 'quantity': 1, 'artwork': '195023952974065531'}]</t>
+        </is>
+      </c>
+      <c r="E1859" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1859" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 3</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1860" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_CactusDrink', 'quantity': 1, 'artwork': '-6455951455730579533'}]</t>
+        </is>
+      </c>
+      <c r="E1860" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1860" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 4</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1861" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Berries', 'quantity': 1, 'artwork': '-8353441490722436680'}]</t>
+        </is>
+      </c>
+      <c r="E1861" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 5</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1862" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Cactus', 'quantity': 1, 'artwork': '-753459149092522257'}]</t>
+        </is>
+      </c>
+      <c r="E1862" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1862" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 6</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1863" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_ChocolateSyrup', 'quantity': 1, 'artwork': '-4393959457617356499'}]</t>
+        </is>
+      </c>
+      <c r="E1863" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 7</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1864" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Jam', 'quantity': 1, 'artwork': '5821576994495228222'}]</t>
+        </is>
+      </c>
+      <c r="E1864" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 8</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1865" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Soda', 'quantity': 1, 'artwork': '-4226886939185924720'}]</t>
+        </is>
+      </c>
+      <c r="E1865" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>Recipe_Cocktail 9</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="C1866" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>[{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Banana', 'quantity': 1, 'artwork': '2193929057029675769'}]</t>
+        </is>
+      </c>
+      <c r="E1866" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48627,7 +48965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FF188"/>
+  <dimension ref="A1:FF192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -50275,6 +50613,11 @@
           <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Item_ShrewSkin', 'quantity': 2, 'artwork': '5679605845456124650'}]}</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Item_LizardSkin', 'quantity': 2, 'artwork': '-2438037773057512394'}]}</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -59845,6 +60188,94 @@
       <c r="D188" t="inlineStr">
         <is>
           <t>{'quantity': 5, 'itemsNeeded': [{'name': 'Item_HolyWater', 'quantity': 1, 'artwork': '8470882321417267426'}, {'name': 'Item_Sugar', 'quantity': 1, 'artwork': '-760002536937637001'}, {'name': 'Item_LizardBladder', 'quantity': 1, 'artwork': '-6548577578586404959'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>Enchantment_SacredGround</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Enchantment_Earth', 'quantity': 1, 'artwork': '-5272188385312275718'}, {'name': 'Enchantment_Light', 'quantity': 1, 'artwork': '2352091176121211133'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>Enchantment_FoulFate</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Enchantment_Dark', 'quantity': 2, 'artwork': '7954706189709371483'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Enchantment_Pollen</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>{'quantity': 1, 'itemsNeeded': [{'name': 'Enchantment_Nature', 'quantity': 1, 'artwork': '2645463031653542284'}, {'name': 'Enchantment_Poison', 'quantity': 1, 'artwork': '992235308759174831'}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>Item_Cocktail</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Coffee', 'quantity': 1, 'artwork': '4121941290723269396'}]}</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_BananaSulfs', 'quantity': 1, 'artwork': '195023952974065531'}]}</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_CactusDrink', 'quantity': 1, 'artwork': '-6455951455730579533'}]}</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Berries', 'quantity': 1, 'artwork': '-8353441490722436680'}]}</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Cactus', 'quantity': 1, 'artwork': '-753459149092522257'}]}</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_ChocolateSyrup', 'quantity': 1, 'artwork': '-4393959457617356499'}]}</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Jam', 'quantity': 1, 'artwork': '5821576994495228222'}]}</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Soda', 'quantity': 1, 'artwork': '-4226886939185924720'}]}</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>{'quantity': 3, 'itemsNeeded': [{'name': 'Item_Liquor', 'quantity': 1, 'artwork': '-2386317588911155238'}, {'name': 'Item_Banana', 'quantity': 1, 'artwork': '2193929057029675769'}]}</t>
         </is>
       </c>
     </row>
